--- a/rules/CORE-000843/negative/01/data/unit-test-coreid-CG0214-negative.xlsx
+++ b/rules/CORE-000843/negative/01/data/unit-test-coreid-CG0214-negative.xlsx
@@ -88,6 +88,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -468,7 +469,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
       <c r="B2" s="4" t="str">
@@ -495,18 +496,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Subject Visits</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="4" t="str">
         <v>tv.xpt</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>Trial Visits</v>
       </c>
     </row>
@@ -519,7 +520,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -542,48 +543,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>SVUPDES</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
         <v>UNSCHEDULED LABS</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="str">
+      <c r="E3" s="4" t="str">
         <v>VISITNUM</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>VISIT</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v>WEEK 4: UNSCHEDULED 01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -783,40 +804,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B6" s="6" t="str">
+      <c r="A6" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="4" t="str">
         <v>SV</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="4" t="str">
         <v>SCREENING 2</v>
       </c>
-      <c r="F6" s="6" t="str">
+      <c r="F6" s="4" t="str">
         <v>Y</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="4" t="str">
         <v>-3</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="4" t="str">
         <v>2012-11-28</v>
       </c>
-      <c r="I6" s="6" t="str">
+      <c r="I6" s="4" t="str">
         <v>2012-11-28</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>-2</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>-2</v>
       </c>
-      <c r="L6" s="6" t="str">
+      <c r="L6" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -859,40 +880,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B8" s="6" t="str">
+      <c r="A8" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="4" t="str">
         <v>SV</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="str">
+      <c r="E8" s="4" t="str">
         <v>WEEK 2</v>
       </c>
-      <c r="F8" s="6" t="str">
+      <c r="F8" s="4" t="str">
         <v>Y</v>
       </c>
-      <c r="G8" s="6" t="str">
+      <c r="G8" s="4" t="str">
         <v>15</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="4" t="str">
         <v>2012-12-13</v>
       </c>
-      <c r="I8" s="6" t="str">
+      <c r="I8" s="4" t="str">
         <v>2012-12-13</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>14</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>14</v>
       </c>
-      <c r="L8" s="6" t="str">
+      <c r="L8" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -935,40 +956,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B10" s="6" t="str">
+      <c r="A10" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B10" s="4" t="str">
         <v>SV</v>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>5</v>
       </c>
-      <c r="E10" s="6" t="str">
+      <c r="E10" s="7" t="str">
         <v>WEEK 4: UNSCHEDULED 01</v>
       </c>
-      <c r="F10" s="6" t="str">
+      <c r="F10" s="4" t="str">
         <v>Y</v>
       </c>
-      <c r="G10" s="6" t="str">
-        <v/>
-      </c>
-      <c r="H10" s="6" t="str">
+      <c r="G10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H10" s="4" t="str">
         <v>2012-12-28</v>
       </c>
-      <c r="I10" s="6" t="str">
+      <c r="I10" s="4" t="str">
         <v>2012-12-28</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>29</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>29</v>
       </c>
-      <c r="L10" s="7" t="str">
+      <c r="L10" s="6" t="str">
         <v>UNSCHEDULED LABS</v>
       </c>
     </row>
@@ -1011,40 +1032,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B12" s="6" t="str">
+      <c r="A12" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B12" s="4" t="str">
         <v>SV</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>8</v>
       </c>
-      <c r="E12" s="6" t="str">
+      <c r="E12" s="4" t="str">
         <v>WEEK 8</v>
       </c>
-      <c r="F12" s="6" t="str">
+      <c r="F12" s="4" t="str">
         <v>Y</v>
       </c>
-      <c r="G12" s="6" t="str">
+      <c r="G12" s="4" t="str">
         <v>57</v>
       </c>
-      <c r="H12" s="6" t="str">
+      <c r="H12" s="4" t="str">
         <v>2013-01-23</v>
       </c>
-      <c r="I12" s="6" t="str">
+      <c r="I12" s="4" t="str">
         <v>2013-01-23</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>55</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>55</v>
       </c>
-      <c r="L12" s="6" t="str">
+      <c r="L12" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -1175,25 +1196,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B6" s="6" t="str">
+      <c r="A6" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B6" s="4" t="str">
         <v>TV</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="str">
+      <c r="D6" s="4" t="str">
         <v>SCREENING 2</v>
       </c>
-      <c r="E6" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F6" s="6" t="str">
+      <c r="E6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F6" s="4" t="str">
         <v>Day Before Initial Study Treatment</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -1221,25 +1242,25 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B8" s="6" t="str">
+      <c r="A8" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B8" s="4" t="str">
         <v>TV</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="4" t="str">
         <v>WEEK 2</v>
       </c>
-      <c r="E8" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F8" s="6" t="str">
+      <c r="E8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F8" s="4" t="str">
         <v>2 Weeks After Start of Study Treatment</v>
       </c>
-      <c r="G8" s="6" t="str">
+      <c r="G8" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -1267,25 +1288,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B10" s="6" t="str">
+      <c r="A10" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B10" s="4" t="str">
         <v>TV</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>7</v>
       </c>
-      <c r="D10" s="6" t="str">
+      <c r="D10" s="4" t="str">
         <v>WEEK 6</v>
       </c>
-      <c r="E10" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F10" s="6" t="str">
+      <c r="E10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
         <v>6 Weeks After Start of Study Treatment</v>
       </c>
-      <c r="G10" s="6" t="str">
+      <c r="G10" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -1313,25 +1334,25 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B12" s="6" t="str">
+      <c r="A12" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B12" s="4" t="str">
         <v>TV</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>9</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D12" s="4" t="str">
         <v>WEEK 12</v>
       </c>
-      <c r="E12" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F12" s="6" t="str">
+      <c r="E12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F12" s="4" t="str">
         <v>12 Weeks After Start of Study Treatment</v>
       </c>
-      <c r="G12" s="6" t="str">
+      <c r="G12" s="4" t="str">
         <v/>
       </c>
     </row>
@@ -1359,25 +1380,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B14" s="6" t="str">
+      <c r="A14" s="4" t="str">
+        <v>CDISCPILOT01</v>
+      </c>
+      <c r="B14" s="4" t="str">
         <v>TV</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>11</v>
       </c>
-      <c r="D14" s="6" t="str">
+      <c r="D14" s="4" t="str">
         <v>WEEK 20</v>
       </c>
-      <c r="E14" s="6" t="str">
-        <v/>
-      </c>
-      <c r="F14" s="6" t="str">
+      <c r="E14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="F14" s="4" t="str">
         <v>20 Weeks After Start of Study Treatment</v>
       </c>
-      <c r="G14" s="6" t="str">
+      <c r="G14" s="4" t="str">
         <v/>
       </c>
     </row>
